--- a/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第七支部委员会-党费收缴子表.xlsx
+++ b/output/2026年4月/党费收缴子表/2026年4月-中共新疆大学计算机科学与技术学院本科生第七支部委员会-党费收缴子表.xlsx
@@ -587,7 +587,7 @@
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="D4" s="4" t="n">
         <v>0</v>
@@ -620,10 +620,10 @@
         <v>0</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>0</v>
+        <v>1136</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="5">
@@ -636,7 +636,7 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>0</v>
@@ -669,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0</v>
+        <v>1137</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="6">
@@ -685,7 +685,7 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>1138</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -718,10 +718,10 @@
         <v>0</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>1138</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="7">
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0</v>
+        <v>1139</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>0</v>
@@ -767,10 +767,10 @@
         <v>0</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0</v>
+        <v>1139</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="8">
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -816,10 +816,10 @@
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0</v>
+        <v>1140</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="9">
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1141</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -865,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0</v>
+        <v>1141</v>
       </c>
       <c r="O9" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="10">
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="D10" s="4" t="n">
         <v>0</v>
@@ -914,10 +914,10 @@
         <v>0</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0</v>
+        <v>1142</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="11">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>0</v>
+        <v>1143</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>0</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0</v>
+        <v>1143</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="12">
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0</v>
+        <v>1144</v>
       </c>
       <c r="D12" s="4" t="n">
         <v>0</v>
@@ -1012,10 +1012,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0</v>
+        <v>1144</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="13">
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="14">
@@ -1077,7 +1077,7 @@
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="D14" s="4" t="n">
         <v>0</v>
@@ -1110,10 +1110,10 @@
         <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0</v>
+        <v>1146</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="15">
@@ -1136,7 +1136,7 @@
       <c r="M15" s="8" t="n"/>
       <c r="N15" s="8" t="n"/>
       <c r="O15" s="3" t="n">
-        <v>0</v>
+        <v>62.70000000000002</v>
       </c>
     </row>
   </sheetData>
